--- a/90_管理/課題リスト.xlsx
+++ b/90_管理/課題リスト.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\20_設計書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AD583D-3EB9-41F1-A39F-C95530AA1CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DEA32C-EAE9-4D1D-92A8-CF7FC6E1E740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4380" yWindow="0" windowWidth="24480" windowHeight="15585" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="210" yWindow="1560" windowWidth="24360" windowHeight="13200" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="課題リスト" sheetId="78" r:id="rId1"/>
@@ -19,6 +19,7 @@
   <definedNames>
     <definedName name="_2a1_" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="_a1" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">課題リスト!$A$1:$G$26</definedName>
     <definedName name="_Order1" hidden="1">255</definedName>
     <definedName name="a" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="AAA" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
@@ -81,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="80">
   <si>
     <t>項番</t>
     <rPh sb="0" eb="2">
@@ -842,8 +843,480 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
+    <t>トップ画面リンクを追加</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>※こちらのメールに返信はできません。不明な点などございましたら、担当者へお問い合わせください</t>
+  </si>
+  <si>
+    <t>色変更のほかに太字を想定、リンク挿入機能は検討中。
+デモ画面の書式設定でOK</t>
+    <rPh sb="0" eb="3">
+      <t>イロヘンコウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>フトジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>ソウニュウキノウ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>ケントウチュウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ショシキ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>CSVダウンロードボタンを追加しました。
+CSV出力内容は現在詳細に表示されているデータ</t>
+    <rPh sb="13" eb="15">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>画面はデモ画面ままでOK</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t xml:space="preserve">リンクは別で管理する方法に変更。化学物質データ画面から遷移するためのボタンは削除しました。
+管理画面メニュー不要。URLのみを通知する。ヒロセネットワークからのみアクセス可能。
+</t>
+    <rPh sb="4" eb="5">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>カガクブッシツ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="46" eb="50">
+      <t>カンリガメン</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>CSVの項目名も日英併記に変更しました。
+日英はヘッダを/区切りの1行とする</t>
+    <rPh sb="4" eb="6">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ニチエイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヘイキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ニチエイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>クギ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ギョウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>ヒロセから送付いただく</t>
+    <rPh sb="5" eb="7">
+      <t>ソウフ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>申請確認画面はエラー無いので不要</t>
+    <rPh sb="0" eb="2">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>表組を広げました。
+表にこだわらず企業名が長いので、企業名とエンドユーザは別行で目立つように</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウグミ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>キギョウメイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>キギョウメイ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>メダ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>CLを以下形式のリンクに変換する
+https://www.hirose.com/ja/product/p/CL0665-0002-0-76</t>
+    <rPh sb="3" eb="5">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヘンカン</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>指摘でいただいた表形式に変更しました。
+申請完了メールと同じ内容を表示する</t>
+    <rPh sb="0" eb="2">
+      <t>シテキ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ヒョウケイシキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>CSVは原則全て日英併記</t>
+    <rPh sb="4" eb="6">
+      <t>ゲンソク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ニチエイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヘイキ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>移行データについて</t>
+    <rPh sb="0" eb="2">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>移行方針の確認</t>
+    <rPh sb="0" eb="2">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウシン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>データ移行は不要。過去データは過去システムから参照する。</t>
+    <rPh sb="3" eb="5">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>HRSロゴ</t>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>パンくず</t>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>パンくず必要か？</t>
+    <rPh sb="4" eb="6">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>リンク先は？</t>
+    <rPh sb="3" eb="4">
+      <t>サキ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>ヒロセホームページとする。https://www.hirose.com/ja/product</t>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>確認中</t>
+    <rPh sb="0" eb="3">
+      <t>カクニンチュウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>バッチを利用しない方法で更新できる方法を取ります。
+→製品マスタを使っている箇所は全て削除する</t>
+    <rPh sb="4" eb="6">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>カショ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>対応中</t>
+    <rPh sb="0" eb="3">
+      <t>タイオウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>ヒロセ/AA</t>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">バッチを利用しない方法で更新できる方法を取ります。
+      <t xml:space="preserve">パンくずの仕様は以下の通りとする。
+ホーム画面: ホーム (リンクなし)
+申請画面: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ホーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> &gt; 化学物質データ申請
+申請確認画面: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ホーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> &gt; 化学物質データ申請確認
+申請完了画面: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ホーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> &gt; 化学物質データ申請完了</t>
+    </r>
+    <rPh sb="5" eb="7">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">①3シート参照
 </t>
     </r>
     <r>
@@ -854,396 +1327,83 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>→製品マスタを使っている箇所は全て削除する</t>
+      <t>→取込完了メールにトップ画面リンクを追加、とありましたが本システムは新ヒロセWebリンクからのログインになるので、メールからトップ画面リンクを押下してもログインエラーになります。メールからトップ画面リンクは削除して良いでしょうか？</t>
     </r>
-    <rPh sb="4" eb="6">
-      <t>リヨウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ホウホウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ホウホウ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>セイヒン</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>カショ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>スベ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>トップ画面リンクを追加</t>
-    <rPh sb="3" eb="5">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>①3シート参照
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
 ②申請完了メールは設計書参照</t>
+    </r>
     <rPh sb="5" eb="7">
       <t>サンショウ</t>
     </rPh>
     <rPh sb="9" eb="11">
-      <t>シンセイ</t>
+      <t>トリコミ</t>
     </rPh>
     <rPh sb="11" eb="13">
       <t>カンリョウ</t>
     </rPh>
-    <rPh sb="17" eb="19">
+    <rPh sb="20" eb="22">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="105" eb="107">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="115" eb="116">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="127" eb="129">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="133" eb="135">
       <t>セッケイ</t>
     </rPh>
-    <rPh sb="19" eb="20">
+    <rPh sb="135" eb="136">
       <t>ショ</t>
     </rPh>
-    <rPh sb="20" eb="22">
+    <rPh sb="136" eb="138">
       <t>サンショウ</t>
     </rPh>
     <phoneticPr fontId="40"/>
   </si>
   <si>
-    <t>※こちらのメールに返信はできません。不明な点などございましたら、担当者へお問い合わせください</t>
-  </si>
-  <si>
-    <t>色変更のほかに太字を想定、リンク挿入機能は検討中。
-デモ画面の書式設定でOK</t>
-    <rPh sb="0" eb="3">
-      <t>イロヘンコウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>フトジ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ソウテイ</t>
-    </rPh>
-    <rPh sb="16" eb="20">
-      <t>ソウニュウキノウ</t>
-    </rPh>
-    <rPh sb="21" eb="24">
-      <t>ケントウチュウ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ショシキ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>セッテイ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>CSVダウンロードボタンを追加しました。
-CSV出力内容は現在詳細に表示されているデータ</t>
-    <rPh sb="13" eb="15">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>画面はデモ画面ままでOK</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t xml:space="preserve">リンクは別で管理する方法に変更。化学物質データ画面から遷移するためのボタンは削除しました。
-管理画面メニュー不要。URLのみを通知する。ヒロセネットワークからのみアクセス可能。
-</t>
-    <rPh sb="4" eb="5">
-      <t>ベツ</t>
+    <t>API受領。仕様調整中</t>
+    <rPh sb="3" eb="5">
+      <t>ジュリョウ</t>
     </rPh>
     <rPh sb="6" eb="8">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ホウホウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="16" eb="20">
-      <t>カガクブッシツ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>センイ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="46" eb="50">
-      <t>カンリガメン</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>フヨウ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>ツウチ</t>
-    </rPh>
-    <rPh sb="85" eb="87">
-      <t>カノウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>CSVの項目名も日英併記に変更しました。
-日英はヘッダを/区切りの1行とする</t>
-    <rPh sb="4" eb="6">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ニチエイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヘイキ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ニチエイ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>クギ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ギョウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>ヒロセから送付いただく</t>
-    <rPh sb="5" eb="7">
-      <t>ソウフ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>申請確認画面はエラー無いので不要</t>
-    <rPh sb="0" eb="2">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>フヨウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>表組を広げました。
-表にこだわらず企業名が長いので、企業名とエンドユーザは別行で目立つように</t>
-    <rPh sb="0" eb="2">
-      <t>ヒョウグミ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ヒロ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ヒョウ</t>
-    </rPh>
-    <rPh sb="17" eb="20">
-      <t>キギョウメイ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ナガ</t>
-    </rPh>
-    <rPh sb="26" eb="29">
-      <t>キギョウメイ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>ギョウ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>メダ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>CLを以下形式のリンクに変換する
-https://www.hirose.com/ja/product/p/CL0665-0002-0-76</t>
-    <rPh sb="3" eb="5">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ケイシキ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ヘンカン</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>指摘でいただいた表形式に変更しました。
-申請完了メールと同じ内容を表示する</t>
-    <rPh sb="0" eb="2">
-      <t>シテキ</t>
+      <t>シヨウ</t>
     </rPh>
     <rPh sb="8" eb="11">
-      <t>ヒョウケイシキ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>CSVは原則全て日英併記</t>
-    <rPh sb="4" eb="6">
-      <t>ゲンソク</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>スベ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ニチエイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヘイキ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>移行データについて</t>
-    <rPh sb="0" eb="2">
-      <t>イコウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>移行方針の確認</t>
-    <rPh sb="0" eb="2">
-      <t>イコウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ホウシン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>データ移行は不要。過去データは過去システムから参照する。</t>
-    <rPh sb="3" eb="5">
-      <t>イコウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>フヨウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>サンショウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>HRSロゴ</t>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>パンくず</t>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>パンくず必要か？</t>
-    <rPh sb="4" eb="6">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>必要</t>
-    <rPh sb="0" eb="2">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>リンク先は？</t>
-    <rPh sb="3" eb="4">
-      <t>サキ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>ヒロセホームページとする。https://www.hirose.com/ja/product</t>
+      <t>チョウセイチュウ</t>
+    </rPh>
     <phoneticPr fontId="40"/>
   </si>
 </sst>
@@ -1256,7 +1416,7 @@
     <numFmt numFmtId="177" formatCode="0.00_)"/>
     <numFmt numFmtId="178" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="48">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1578,6 +1738,20 @@
     <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
@@ -2227,7 +2401,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2257,6 +2431,12 @@
     </xf>
     <xf numFmtId="0" fontId="43" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="186">
@@ -2904,6 +3084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7D65F84-4143-485E-A686-A2B54498E502}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -2937,7 +3118,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="24">
+    <row r="2" spans="1:7" ht="24" hidden="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -2950,8 +3131,8 @@
       <c r="D2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>52</v>
+      <c r="E2" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
@@ -2973,7 +3154,9 @@
       <c r="D3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="9"/>
+      <c r="E3" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="F3" s="2" t="s">
         <v>5</v>
       </c>
@@ -2981,7 +3164,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="48">
+    <row r="4" spans="1:7" ht="72">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -2995,16 +3178,16 @@
         <v>9</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="24">
+    <row r="5" spans="1:7" ht="24" hidden="1">
       <c r="A5" s="4">
         <v>5</v>
       </c>
@@ -3018,7 +3201,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>12</v>
@@ -3027,7 +3210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" hidden="1">
       <c r="A6" s="5">
         <v>6</v>
       </c>
@@ -3050,7 +3233,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="27.75" customHeight="1">
+    <row r="7" spans="1:7" ht="27.75" hidden="1" customHeight="1">
       <c r="A7" s="4">
         <v>7</v>
       </c>
@@ -3073,7 +3256,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="24">
+    <row r="8" spans="1:7" ht="24" hidden="1">
       <c r="A8" s="5">
         <v>8</v>
       </c>
@@ -3087,7 +3270,7 @@
         <v>11</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>12</v>
@@ -3096,7 +3279,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" hidden="1">
       <c r="A9" s="4">
         <v>9</v>
       </c>
@@ -3110,7 +3293,7 @@
         <v>11</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>12</v>
@@ -3119,7 +3302,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="60">
+    <row r="10" spans="1:7" ht="60.75" customHeight="1">
       <c r="A10" s="5">
         <v>10</v>
       </c>
@@ -3133,16 +3316,16 @@
         <v>11</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="24">
+    <row r="11" spans="1:7" ht="24" hidden="1">
       <c r="A11" s="4">
         <v>11</v>
       </c>
@@ -3156,7 +3339,7 @@
         <v>11</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>12</v>
@@ -3165,7 +3348,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="24">
+    <row r="12" spans="1:7" ht="24" hidden="1">
       <c r="A12" s="5">
         <v>12</v>
       </c>
@@ -3188,7 +3371,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="24">
+    <row r="13" spans="1:7" ht="24" hidden="1">
       <c r="A13" s="4">
         <v>13</v>
       </c>
@@ -3202,7 +3385,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>11</v>
@@ -3211,7 +3394,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" hidden="1">
       <c r="A14" s="5">
         <v>14</v>
       </c>
@@ -3225,7 +3408,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>12</v>
@@ -3234,7 +3417,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="36">
+    <row r="15" spans="1:7" ht="36" hidden="1">
       <c r="A15" s="4">
         <v>15</v>
       </c>
@@ -3248,7 +3431,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>12</v>
@@ -3257,7 +3440,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="24">
+    <row r="16" spans="1:7" ht="36.75" hidden="1" customHeight="1">
       <c r="A16" s="5">
         <v>16</v>
       </c>
@@ -3271,14 +3454,16 @@
         <v>11</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="2"/>
+      <c r="G16" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" hidden="1">
       <c r="A17" s="4">
         <v>17</v>
       </c>
@@ -3301,7 +3486,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" hidden="1">
       <c r="A18" s="5">
         <v>18</v>
       </c>
@@ -3324,7 +3509,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" hidden="1">
       <c r="A19" s="4">
         <v>19</v>
       </c>
@@ -3347,7 +3532,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="24">
+    <row r="20" spans="1:7" ht="24" hidden="1">
       <c r="A20" s="5">
         <v>20</v>
       </c>
@@ -3361,7 +3546,7 @@
         <v>11</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>12</v>
@@ -3370,7 +3555,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="21.6" customHeight="1">
+    <row r="21" spans="1:7" ht="21.6" hidden="1" customHeight="1">
       <c r="A21" s="4">
         <v>21</v>
       </c>
@@ -3393,7 +3578,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="21.6" customHeight="1">
+    <row r="22" spans="1:7" ht="21.6" hidden="1" customHeight="1">
       <c r="A22" s="5">
         <v>22</v>
       </c>
@@ -3416,7 +3601,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="21.6" customHeight="1">
+    <row r="23" spans="1:7" ht="21.6" hidden="1" customHeight="1">
       <c r="A23" s="5">
         <v>24</v>
       </c>
@@ -3430,7 +3615,7 @@
         <v>9</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>5</v>
@@ -3439,21 +3624,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="21.6" customHeight="1">
+    <row r="24" spans="1:7" ht="21.6" hidden="1" customHeight="1">
       <c r="A24" s="4">
         <v>25</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -3462,21 +3647,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="21.6" customHeight="1">
+    <row r="25" spans="1:7" ht="21.6" hidden="1" customHeight="1">
       <c r="A25" s="4">
         <v>25</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -3485,21 +3670,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="21.6" customHeight="1">
+    <row r="26" spans="1:7" ht="61.5" hidden="1" customHeight="1">
       <c r="A26" s="4">
         <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>73</v>
+      <c r="E26" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -3509,6 +3694,15 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G26" xr:uid="{F7D65F84-4143-485E-A686-A2B54498E502}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="確認中"/>
+        <filter val="検討中"/>
+        <filter val="対応中"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="40"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3521,17 +3715,18 @@
   <sheetData>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="40"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/90_管理/課題リスト.xlsx
+++ b/90_管理/課題リスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DEA32C-EAE9-4D1D-92A8-CF7FC6E1E740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{BD28298F-57A0-474A-8ACA-719FD4E4AED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="210" yWindow="1560" windowWidth="24360" windowHeight="13200" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,6 +62,7 @@
     <definedName name="画面遷移new" hidden="1">{"'画面仕様'!$C$22:$BY$40","'画面仕様'!$C$28:$BY$39"}</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1307,10 +1308,7 @@
       <t>シンセイ</t>
     </rPh>
     <rPh sb="90" eb="92">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="111" eb="113">
-      <t>カンリョウ</t>
+      <t>カンリョウカンリョウ</t>
     </rPh>
     <phoneticPr fontId="40"/>
   </si>

--- a/90_管理/課題リスト.xlsx
+++ b/90_管理/課題リスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{BD28298F-57A0-474A-8ACA-719FD4E4AED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA6F87E-D81A-437E-B1E7-35DC3EDDB11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="1560" windowWidth="24360" windowHeight="13200" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="345" windowWidth="23520" windowHeight="13065" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="課題リスト" sheetId="78" r:id="rId1"/>
@@ -62,7 +62,6 @@
     <definedName name="画面遷移new" hidden="1">{"'画面仕様'!$C$22:$BY$40","'画面仕様'!$C$28:$BY$39"}</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1313,6 +1312,19 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
+    <t>API受領。仕様調整中</t>
+    <rPh sb="3" eb="5">
+      <t>ジュリョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>チョウセイチュウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">①3シート参照
 </t>
@@ -1325,7 +1337,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>→取込完了メールにトップ画面リンクを追加、とありましたが本システムは新ヒロセWebリンクからのログインになるので、メールからトップ画面リンクを押下してもログインエラーになります。メールからトップ画面リンクは削除して良いでしょうか？</t>
+      <t>→取込完了メールにトップ画面リンクを追加、とありましたが本システムは新ヒロセWebリンクからのログインになるので、メールからトップ画面リンクを押下してもログインエラーになります。メールからトップ画面リンクは削除して良いでしょうか？⇒新Webログイン画面リンクとする。URLはヒロセ待ち</t>
     </r>
     <r>
       <rPr>
@@ -1374,33 +1386,29 @@
     <rPh sb="115" eb="116">
       <t>ヨ</t>
     </rPh>
-    <rPh sb="125" eb="127">
+    <rPh sb="124" eb="125">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="132" eb="134">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="148" eb="149">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="152" eb="154">
       <t>シンセイ</t>
     </rPh>
-    <rPh sb="127" eb="129">
+    <rPh sb="154" eb="156">
       <t>カンリョウ</t>
     </rPh>
-    <rPh sb="133" eb="135">
+    <rPh sb="160" eb="162">
       <t>セッケイ</t>
     </rPh>
-    <rPh sb="135" eb="136">
+    <rPh sb="162" eb="163">
       <t>ショ</t>
     </rPh>
-    <rPh sb="136" eb="138">
+    <rPh sb="163" eb="165">
       <t>サンショウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>API受領。仕様調整中</t>
-    <rPh sb="3" eb="5">
-      <t>ジュリョウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>チョウセイチュウ</t>
     </rPh>
     <phoneticPr fontId="40"/>
   </si>
@@ -3153,7 +3161,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>5</v>
@@ -3176,7 +3184,7 @@
         <v>9</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>

--- a/90_管理/課題リスト.xlsx
+++ b/90_管理/課題リスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA6F87E-D81A-437E-B1E7-35DC3EDDB11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8496AFBD-356F-4B1F-B030-BBAC7679BA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="345" windowWidth="23520" windowHeight="13065" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4635" yWindow="690" windowWidth="23520" windowHeight="13065" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="課題リスト" sheetId="78" r:id="rId1"/>
@@ -1337,7 +1337,8 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>→取込完了メールにトップ画面リンクを追加、とありましたが本システムは新ヒロセWebリンクからのログインになるので、メールからトップ画面リンクを押下してもログインエラーになります。メールからトップ画面リンクは削除して良いでしょうか？⇒新Webログイン画面リンクとする。URLはヒロセ待ち</t>
+      <t>→取込完了メールにトップ画面リンクを追加、とありましたが本システムは新ヒロセWebリンクからのログインになるので、メールからトップ画面リンクを押下してもログインエラーになります。メールからトップ画面リンクは削除して良いでしょうか？⇒新Webログイン画面リンクとする。https://www.hirose.com/ja/product/login
+https://www.hirose.com/en/product/login</t>
     </r>
     <r>
       <rPr>
@@ -1392,22 +1393,19 @@
     <rPh sb="132" eb="134">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="148" eb="149">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="152" eb="154">
+    <rPh sb="222" eb="224">
       <t>シンセイ</t>
     </rPh>
-    <rPh sb="154" eb="156">
+    <rPh sb="224" eb="226">
       <t>カンリョウ</t>
     </rPh>
-    <rPh sb="160" eb="162">
+    <rPh sb="230" eb="232">
       <t>セッケイ</t>
     </rPh>
-    <rPh sb="162" eb="163">
+    <rPh sb="232" eb="233">
       <t>ショ</t>
     </rPh>
-    <rPh sb="163" eb="165">
+    <rPh sb="233" eb="235">
       <t>サンショウ</t>
     </rPh>
     <phoneticPr fontId="40"/>
@@ -3170,7 +3168,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="72">
+    <row r="4" spans="1:7" ht="96">
       <c r="A4" s="4">
         <v>3</v>
       </c>

--- a/90_管理/課題リスト.xlsx
+++ b/90_管理/課題リスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8496AFBD-356F-4B1F-B030-BBAC7679BA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FECA4D7-415E-46FB-A4DD-52E83F0BD1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4635" yWindow="690" windowWidth="23520" windowHeight="13065" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="930" yWindow="1635" windowWidth="27585" windowHeight="13065" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="課題リスト" sheetId="78" r:id="rId1"/>
@@ -1312,19 +1312,6 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
-    <t>API受領。仕様調整中</t>
-    <rPh sb="3" eb="5">
-      <t>ジュリョウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>チョウセイチュウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">①3シート参照
 </t>
@@ -1407,6 +1394,20 @@
     </rPh>
     <rPh sb="233" eb="235">
       <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>API受領。
+2026/6/25 仕様確定</t>
+    <rPh sb="3" eb="5">
+      <t>ジュリョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カクテイ</t>
     </rPh>
     <phoneticPr fontId="40"/>
   </si>
@@ -3145,7 +3146,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" ht="24">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -3159,7 +3160,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>5</v>
@@ -3182,7 +3183,7 @@
         <v>9</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>

--- a/90_管理/課題リスト.xlsx
+++ b/90_管理/課題リスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FECA4D7-415E-46FB-A4DD-52E83F0BD1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D85F44-7E11-40BC-BDD0-F9AF37A05DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="1635" windowWidth="27585" windowHeight="13065" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1935" yWindow="0" windowWidth="23085" windowHeight="15585" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="課題リスト" sheetId="78" r:id="rId1"/>

--- a/90_管理/課題リスト.xlsx
+++ b/90_管理/課題リスト.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D85F44-7E11-40BC-BDD0-F9AF37A05DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{3FECA4D7-415E-46FB-A4DD-52E83F0BD1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCF5BB7C-591C-4837-A13F-7F7CBEF50666}"/>
   <bookViews>
-    <workbookView xWindow="1935" yWindow="0" windowWidth="23085" windowHeight="15585" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="930" yWindow="1635" windowWidth="27585" windowHeight="13065" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="課題リスト" sheetId="78" r:id="rId1"/>
@@ -61,8 +61,11 @@
     <definedName name="荷札イレギュラー" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="画面遷移new" hidden="1">{"'画面仕様'!$C$22:$BY$40","'画面仕様'!$C$28:$BY$39"}</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -74,9 +77,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -111,6 +111,34 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
+    <t>指摘者</t>
+    <rPh sb="0" eb="3">
+      <t>シテキシャ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>対応内容</t>
+    <rPh sb="0" eb="4">
+      <t>タイオウナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>対応者</t>
+    <rPh sb="0" eb="2">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シャ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>ステータス</t>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
     <t>製品マスタ</t>
     <rPh sb="0" eb="2">
       <t>セイヒン</t>
@@ -118,39 +146,220 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
-    <t>指摘者</t>
+    <t>バッチソースが別途必要。見積外なので別途見積必須。</t>
+    <rPh sb="7" eb="9">
+      <t>ベット</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ミツモリガイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ベット</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ミツモリ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>AA</t>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>バッチを利用しない方法で更新できる方法を取ります。
+→製品マスタを使っている箇所は全て削除する</t>
+    <rPh sb="4" eb="6">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>カショ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>ヒロセ</t>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>ログイン機能</t>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>別システムにて行う予定だが、仕様不明のため現状進展がない認識です。</t>
+    <rPh sb="0" eb="1">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>シヨウフメイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シンテン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ニンシキ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>API受領。
+2026/6/25 仕様確定</t>
+    <rPh sb="3" eb="5">
+      <t>ジュリョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カクテイ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>検討中</t>
     <rPh sb="0" eb="3">
-      <t>シテキシャ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>ヒロセ</t>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>対応内容</t>
-    <rPh sb="0" eb="4">
-      <t>タイオウナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>対応者</t>
-    <rPh sb="0" eb="2">
-      <t>タイオウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>シャ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>ステータス</t>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>AA</t>
+      <t>ケントウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>バッチ処理/環境証明書申請完了</t>
+    <rPh sb="3" eb="5">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>環境証明書申請完了時および環境証明書取込バッチ実行時のメール詳細を確認したいため以下の資料をご連携お願いいたします。
+①「SEML020 環境証明書取込完了メール」
+②「SEML030　環境証明書申請完了お知らせメール」</t>
+    <rPh sb="0" eb="7">
+      <t>カンキョウショウメイショシンセイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ショウメイショ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>トリコミ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo UI"/>
+      </rPr>
+      <t xml:space="preserve">①3シート参照
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+      </rPr>
+      <t xml:space="preserve">→取込完了メールにトップ画面リンクを追加、とありましたが本システムは新ヒロセWebリンクからのログインになるので、メールからトップ画面リンクを押下してもログインエラーになります。メールからトップ画面リンクは削除して良いでしょうか？⇒新Webログイン画面リンクとする。https://www.hirose.com/ja/product/login
+https://www.hirose.com/en/product/login
+はい、過去メールと口頭にて回答ずみです、上記で問題ございません。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo UI"/>
+      </rPr>
+      <t>②申請完了メールは設計書参照</t>
+    </r>
+  </si>
+  <si>
+    <t>確認中</t>
+    <rPh sb="0" eb="3">
+      <t>カクニンチュウ</t>
+    </rPh>
     <phoneticPr fontId="40"/>
   </si>
   <si>
@@ -164,15 +373,177 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
+    <t>リッチテキストで太字、リンクの挿入も機能としてほしい。</t>
+    <rPh sb="8" eb="10">
+      <t>フトジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ソウニュウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
     <t>ヒロセ</t>
   </si>
   <si>
+    <t>色変更のほかに太字を想定、リンク挿入機能は検討中。
+デモ画面の書式設定でOK</t>
+    <rPh sb="0" eb="3">
+      <t>イロヘンコウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>フトジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>ソウニュウキノウ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>ケントウチュウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ショシキ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
     <t>AA</t>
   </si>
   <si>
-    <t>完了</t>
+    <t>管理者申請ログ画面</t>
     <rPh sb="0" eb="2">
-      <t>カンリョウ</t>
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>iframeのようなUIは使いにくいのでスクロールは画面全体の1つのみにしてほしい。</t>
+    <rPh sb="13" eb="14">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="26" eb="30">
+      <t>ガメンゼンタイ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>画面全体で1つのスクロールにするように変更しました。</t>
+    <rPh sb="0" eb="4">
+      <t>ガメンゼンタイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>過去3年分の申請ログを保管してほしいです。</t>
+    <rPh sb="0" eb="2">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ネンブン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ホカン</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>現時点ではDBに申請ログのデータを保存して、保存データの削除予定はありません。</t>
+    <rPh sb="0" eb="3">
+      <t>ゲンジテン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>CSVボタンを追加してほしい。</t>
+    <rPh sb="7" eb="9">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>CSVダウンロードボタンを追加しました。
+CSV出力内容は現在詳細に表示されているデータ</t>
+    <rPh sb="13" eb="15">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>期間指定してCSVダウンロードができれば画面確認は不要です。</t>
+    <rPh sb="0" eb="4">
+      <t>キカンシテイ</t>
+    </rPh>
+    <rPh sb="20" eb="24">
+      <t>ガメンカクニン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>画面はデモ画面ままでOK</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
     </rPh>
     <phoneticPr fontId="40"/>
   </si>
@@ -187,31 +558,163 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
-    <t>管理者申請ログ画面</t>
+    <t>化学物質データ画面から遷移するのではなく、別でURLの管理をしたい。</t>
     <rPh sb="0" eb="2">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>シャ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シンセイ</t>
+      <t>カガク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブッシツ</t>
     </rPh>
     <rPh sb="7" eb="9">
       <t>ガメン</t>
     </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>期間指定してCSVダウンロードができれば画面確認は不要です。</t>
+    <rPh sb="11" eb="13">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t xml:space="preserve">リンクは別で管理する方法に変更。化学物質データ画面から遷移するためのボタンは削除しました。
+管理画面メニュー不要。URLのみを通知する。ヒロセネットワークからのみアクセス可能。
+</t>
+    <rPh sb="4" eb="5">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>カガクブッシツ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="46" eb="50">
+      <t>カンリガメン</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>ヒロセ/AA</t>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>対応中</t>
+    <rPh sb="0" eb="3">
+      <t>タイオウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>出力するCSVの項目名も日英併記にしてほしい。</t>
+    <rPh sb="0" eb="2">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>コウモクメイ</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>ニチエイヘイキ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>CSVの項目名も日英併記に変更しました。
+日英はヘッダを/区切りの1行とする</t>
+    <rPh sb="4" eb="6">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ニチエイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヘイキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ニチエイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>クギ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ギョウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>化学物質データ画面～化学物質データ申請完了画面</t>
     <rPh sb="0" eb="4">
-      <t>キカンシテイ</t>
-    </rPh>
-    <rPh sb="20" eb="24">
-      <t>ガメンカクニン</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>フヨウ</t>
+      <t>カガクブッシツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>カガクブッシツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>共通ヘッダーとしてHRSロゴを追加、ロゴを押下で「化学物質データ画面」に遷移するようにしてほしい。</t>
+    <rPh sb="0" eb="2">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="25" eb="29">
+      <t>カガクブッシツ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="40"/>
   </si>
@@ -226,111 +729,37 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
-    <t>化学物質データ画面～化学物質データ申請完了画面</t>
-    <rPh sb="0" eb="4">
-      <t>カガクブッシツ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="10" eb="14">
-      <t>カガクブッシツ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>出力するCSVの項目名も日英併記にしてほしい。</t>
+    <t>指摘レビューにおいてHRSロゴ画像のファイルが文字列となり取込できなかったため、別途画像ファイルをご連携お願いいたします。</t>
     <rPh sb="0" eb="2">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>コウモクメイ</t>
-    </rPh>
-    <rPh sb="12" eb="16">
-      <t>ニチエイヘイキ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>iframeのようなUIは使いにくいのでスクロールは画面全体の1つのみにしてほしい。</t>
-    <rPh sb="13" eb="14">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="26" eb="30">
-      <t>ガメンゼンタイ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>CSVボタンを追加してほしい。</t>
-    <rPh sb="7" eb="9">
-      <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>リッチテキストで太字、リンクの挿入も機能としてほしい。</t>
-    <rPh sb="8" eb="10">
-      <t>フトジ</t>
+      <t>シテキ</t>
     </rPh>
     <rPh sb="15" eb="17">
-      <t>ソウニュウ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>バッチソースが別途必要。見積外なので別途見積必須。</t>
-    <rPh sb="7" eb="9">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>トリコミ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
       <t>ベット</t>
     </rPh>
-    <rPh sb="9" eb="11">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>ミツモリガイ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ベット</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ミツモリ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ヒッス</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>共通ヘッダーとしてHRSロゴを追加、ロゴを押下で「化学物質データ画面」に遷移するようにしてほしい。</t>
-    <rPh sb="0" eb="2">
-      <t>キョウツウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="25" eb="29">
-      <t>カガクブッシツ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>センイ</t>
+    <rPh sb="42" eb="44">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>ヒロセから送付いただく</t>
+    <rPh sb="5" eb="7">
+      <t>ソウフ</t>
     </rPh>
     <phoneticPr fontId="40"/>
   </si>
@@ -370,6 +799,25 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
+    <t>申請確認画面はエラー無いので不要</t>
+    <rPh sb="0" eb="2">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
     <t>提出企業名とエンドユーザーの表組を広げてほしい。</t>
     <rPh sb="0" eb="5">
       <t>テイシュツキギョウメイ</t>
@@ -379,6 +827,38 @@
     </rPh>
     <rPh sb="17" eb="18">
       <t>ヒロ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>表組を広げました。
+表にこだわらず企業名が長いので、企業名とエンドユーザは別行で目立つように</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウグミ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>キギョウメイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>キギョウメイ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>メダ</t>
     </rPh>
     <phoneticPr fontId="40"/>
   </si>
@@ -421,18 +901,16 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
-    <t>過去3年分の申請ログを保管してほしいです。</t>
-    <rPh sb="0" eb="2">
-      <t>カコ</t>
-    </rPh>
+    <t>CLを以下形式のリンクに変換する
+https://www.hirose.com/ja/product/p/CL0665-0002-0-76</t>
     <rPh sb="3" eb="5">
-      <t>ネンブン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ホカン</t>
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヘンカン</t>
     </rPh>
     <phoneticPr fontId="40"/>
   </si>
@@ -453,6 +931,31 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
+    <t>不要の文言箇所に取り消し線を引きました。</t>
+    <rPh sb="0" eb="2">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>モンゴン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カショ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
     <t>代理店権限の処理は不要です。</t>
     <rPh sb="0" eb="3">
       <t>ダイリテン</t>
@@ -469,6 +972,16 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
+    <t>不要のため該当箇所をグレーアウトしました。</t>
+    <rPh sb="0" eb="2">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>ガイトウカショ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
     <t>製品マスタテーブルで不要項目があります。</t>
     <rPh sb="0" eb="2">
       <t>セイヒン</t>
@@ -479,6 +992,19 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
+    <t>項番1より不要のため該当箇所をグレーアウトしました。</t>
+    <rPh sb="0" eb="2">
+      <t>コウバン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>ガイトウカショ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
     <t>化学物質データ申請完了画面</t>
     <rPh sb="0" eb="4">
       <t>カガクブッシツ</t>
@@ -514,6 +1040,35 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
+    <t>指摘でいただいた表形式に変更しました。
+申請完了メールと同じ内容を表示する</t>
+    <rPh sb="0" eb="2">
+      <t>シテキ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ヒョウケイシキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
     <t>送信元メールアドレスは固定です。</t>
     <rPh sb="0" eb="2">
       <t>ソウシン</t>
@@ -579,240 +1134,6 @@
     </rPh>
     <rPh sb="30" eb="32">
       <t>ニンシキ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>ログイン機能</t>
-    <rPh sb="4" eb="6">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>別システムにて行う予定だが、仕様不明のため現状進展がない認識です。</t>
-    <rPh sb="0" eb="1">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ヨテイ</t>
-    </rPh>
-    <rPh sb="14" eb="18">
-      <t>シヨウフメイ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ゲンジョウ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>シンテン</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ニンシキ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>検討中</t>
-    <rPh sb="0" eb="3">
-      <t>ケントウチュウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>化学物質データ画面から遷移するのではなく、別でURLの管理をしたい。</t>
-    <rPh sb="0" eb="2">
-      <t>カガク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ブッシツ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>センイ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>画面全体で1つのスクロールにするように変更しました。</t>
-    <rPh sb="0" eb="4">
-      <t>ガメンゼンタイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ヘンコウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>項番1より不要のため該当箇所をグレーアウトしました。</t>
-    <rPh sb="0" eb="2">
-      <t>コウバン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>フヨウ</t>
-    </rPh>
-    <rPh sb="10" eb="14">
-      <t>ガイトウカショ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>不要のため該当箇所をグレーアウトしました。</t>
-    <rPh sb="0" eb="2">
-      <t>フヨウ</t>
-    </rPh>
-    <rPh sb="5" eb="9">
-      <t>ガイトウカショ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>不要の文言箇所に取り消し線を引きました。</t>
-    <rPh sb="0" eb="2">
-      <t>フヨウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>モンゴン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カショ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ケ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>セン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ヒ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>バッチ処理/環境証明書申請完了</t>
-    <rPh sb="3" eb="5">
-      <t>ショリ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>環境証明書申請完了時および環境証明書取込バッチ実行時のメール詳細を確認したいため以下の資料をご連携お願いいたします。
-①「SEML020 環境証明書取込完了メール」
-②「SEML030　環境証明書申請完了お知らせメール」</t>
-    <rPh sb="0" eb="7">
-      <t>カンキョウショウメイショシンセイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>カンキョウ</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>ショウメイショ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>トリコミ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>シリョウ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>レンケイ</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>ネガ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>現時点ではDBに申請ログのデータを保存して、保存データの削除予定はありません。</t>
-    <rPh sb="0" eb="3">
-      <t>ゲンジテン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ホゾン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ホゾン</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>指摘レビューにおいてHRSロゴ画像のファイルが文字列となり取込できなかったため、別途画像ファイルをご連携お願いいたします。</t>
-    <rPh sb="0" eb="2">
-      <t>シテキ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ガゾウ</t>
-    </rPh>
-    <rPh sb="23" eb="26">
-      <t>モジレツ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>トリコミ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>ベット</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ガゾウ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>レンケイ</t>
-    </rPh>
-    <rPh sb="53" eb="54">
-      <t>ネガ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>「ダウンロードCSVファイルについて」シート。日英併記でしょうか？</t>
-    <rPh sb="23" eb="25">
-      <t>ニチエイ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ヘイキ</t>
     </rPh>
     <phoneticPr fontId="40"/>
   </si>
@@ -843,249 +1164,12 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
-    <t>トップ画面リンクを追加</t>
-    <rPh sb="3" eb="5">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>※こちらのメールに返信はできません。不明な点などございましたら、担当者へお問い合わせください</t>
-  </si>
-  <si>
-    <t>色変更のほかに太字を想定、リンク挿入機能は検討中。
-デモ画面の書式設定でOK</t>
-    <rPh sb="0" eb="3">
-      <t>イロヘンコウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>フトジ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ソウテイ</t>
-    </rPh>
-    <rPh sb="16" eb="20">
-      <t>ソウニュウキノウ</t>
-    </rPh>
-    <rPh sb="21" eb="24">
-      <t>ケントウチュウ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ショシキ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>セッテイ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>CSVダウンロードボタンを追加しました。
-CSV出力内容は現在詳細に表示されているデータ</t>
-    <rPh sb="13" eb="15">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>画面はデモ画面ままでOK</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t xml:space="preserve">リンクは別で管理する方法に変更。化学物質データ画面から遷移するためのボタンは削除しました。
-管理画面メニュー不要。URLのみを通知する。ヒロセネットワークからのみアクセス可能。
-</t>
-    <rPh sb="4" eb="5">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ホウホウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="16" eb="20">
-      <t>カガクブッシツ</t>
-    </rPh>
+    <t>「ダウンロードCSVファイルについて」シート。日英併記でしょうか？</t>
     <rPh sb="23" eb="25">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>センイ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="46" eb="50">
-      <t>カンリガメン</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>フヨウ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>ツウチ</t>
-    </rPh>
-    <rPh sb="85" eb="87">
-      <t>カノウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>CSVの項目名も日英併記に変更しました。
-日英はヘッダを/区切りの1行とする</t>
-    <rPh sb="4" eb="6">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
       <t>ニチエイ</t>
     </rPh>
-    <rPh sb="10" eb="12">
+    <rPh sb="25" eb="27">
       <t>ヘイキ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ニチエイ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>クギ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ギョウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>ヒロセから送付いただく</t>
-    <rPh sb="5" eb="7">
-      <t>ソウフ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>申請確認画面はエラー無いので不要</t>
-    <rPh sb="0" eb="2">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>フヨウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>表組を広げました。
-表にこだわらず企業名が長いので、企業名とエンドユーザは別行で目立つように</t>
-    <rPh sb="0" eb="2">
-      <t>ヒョウグミ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ヒロ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ヒョウ</t>
-    </rPh>
-    <rPh sb="17" eb="20">
-      <t>キギョウメイ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ナガ</t>
-    </rPh>
-    <rPh sb="26" eb="29">
-      <t>キギョウメイ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>ギョウ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>メダ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>CLを以下形式のリンクに変換する
-https://www.hirose.com/ja/product/p/CL0665-0002-0-76</t>
-    <rPh sb="3" eb="5">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ケイシキ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ヘンカン</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>指摘でいただいた表形式に変更しました。
-申請完了メールと同じ内容を表示する</t>
-    <rPh sb="0" eb="2">
-      <t>シテキ</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>ヒョウケイシキ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="40"/>
   </si>
@@ -1149,6 +1233,17 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
+    <t>リンク先は？</t>
+    <rPh sb="3" eb="4">
+      <t>サキ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>ヒロセホームページとする。https://www.hirose.com/ja/product</t>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
     <t>パンくず</t>
     <phoneticPr fontId="40"/>
   </si>
@@ -1157,70 +1252,6 @@
     <rPh sb="4" eb="6">
       <t>ヒツヨウ</t>
     </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>リンク先は？</t>
-    <rPh sb="3" eb="4">
-      <t>サキ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>ヒロセホームページとする。https://www.hirose.com/ja/product</t>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>確認中</t>
-    <rPh sb="0" eb="3">
-      <t>カクニンチュウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>バッチを利用しない方法で更新できる方法を取ります。
-→製品マスタを使っている箇所は全て削除する</t>
-    <rPh sb="4" eb="6">
-      <t>リヨウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ホウホウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ホウホウ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>セイヒン</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>カショ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>スベ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>対応中</t>
-    <rPh sb="0" eb="3">
-      <t>タイオウチュウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>ヒロセ/AA</t>
     <phoneticPr fontId="40"/>
   </si>
   <si>
@@ -1312,104 +1343,17 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">①3シート参照
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>→取込完了メールにトップ画面リンクを追加、とありましたが本システムは新ヒロセWebリンクからのログインになるので、メールからトップ画面リンクを押下してもログインエラーになります。メールからトップ画面リンクは削除して良いでしょうか？⇒新Webログイン画面リンクとする。https://www.hirose.com/ja/product/login
-https://www.hirose.com/en/product/login</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">
-②申請完了メールは設計書参照</t>
-    </r>
-    <rPh sb="5" eb="7">
-      <t>サンショウ</t>
+    <t>トップ画面リンクを追加</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
     </rPh>
     <rPh sb="9" eb="11">
-      <t>トリコミ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="26" eb="28">
       <t>ツイカ</t>
     </rPh>
-    <rPh sb="36" eb="37">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>シン</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="79" eb="81">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="105" eb="107">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="111" eb="113">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="115" eb="116">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="124" eb="125">
-      <t>シン</t>
-    </rPh>
-    <rPh sb="132" eb="134">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="222" eb="224">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="224" eb="226">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="230" eb="232">
-      <t>セッケイ</t>
-    </rPh>
-    <rPh sb="232" eb="233">
-      <t>ショ</t>
-    </rPh>
-    <rPh sb="233" eb="235">
-      <t>サンショウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>API受領。
-2026/6/25 仕様確定</t>
-    <rPh sb="3" eb="5">
-      <t>ジュリョウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>カクテイ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>※こちらのメールに返信はできません。不明な点などございましたら、担当者へお問い合わせください</t>
   </si>
 </sst>
 </file>
@@ -1421,7 +1365,7 @@
     <numFmt numFmtId="177" formatCode="0.00_)"/>
     <numFmt numFmtId="178" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="48">
+  <fonts count="50">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1742,13 +1686,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1760,6 +1697,21 @@
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Meiryo UI"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Meiryo UI"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
     </font>
   </fonts>
   <fills count="13">
@@ -2406,7 +2358,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2437,11 +2389,14 @@
     <xf numFmtId="0" fontId="43" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="186">
@@ -2663,14 +2618,63 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1790700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>2686050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D223EAE-CEAD-DBCC-7B54-769A5C6AFFF3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10239375" y="2362200"/>
+          <a:ext cx="4572000" cy="895350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>657987</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>762</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>76689</xdr:rowOff>
     </xdr:to>
@@ -3093,11 +3097,11 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="4.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.125" customWidth="1"/>
-    <col min="4" max="4" width="9.5" customWidth="1"/>
-    <col min="5" max="5" width="43.875" customWidth="1"/>
+    <col min="3" max="3" width="50.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" customWidth="1"/>
+    <col min="5" max="5" width="43.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21.6" customHeight="1">
@@ -3111,16 +3115,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="24" hidden="1">
@@ -3128,22 +3132,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="24">
@@ -3151,45 +3155,45 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="96">
+    <row r="4" spans="1:7" ht="310.5" customHeight="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>78</v>
+      <c r="E4" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="24" hidden="1">
@@ -3197,22 +3201,22 @@
         <v>5</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" hidden="1">
@@ -3220,22 +3224,22 @@
         <v>6</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="27.75" hidden="1" customHeight="1">
@@ -3243,22 +3247,22 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="24" hidden="1">
@@ -3266,22 +3270,22 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7" hidden="1">
@@ -3289,22 +3293,22 @@
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="60.75" customHeight="1">
@@ -3312,22 +3316,22 @@
         <v>10</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="24" hidden="1">
@@ -3335,22 +3339,22 @@
         <v>11</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="24" hidden="1">
@@ -3358,22 +3362,22 @@
         <v>12</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="24" hidden="1">
@@ -3381,22 +3385,22 @@
         <v>13</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7" hidden="1">
@@ -3404,22 +3408,22 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="36" hidden="1">
@@ -3427,22 +3431,22 @@
         <v>15</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="36.75" hidden="1" customHeight="1">
@@ -3450,22 +3454,22 @@
         <v>16</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7" hidden="1">
@@ -3473,22 +3477,22 @@
         <v>17</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7" hidden="1">
@@ -3496,22 +3500,22 @@
         <v>18</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:7" hidden="1">
@@ -3519,22 +3523,22 @@
         <v>19</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="24" hidden="1">
@@ -3542,22 +3546,22 @@
         <v>20</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="21.6" hidden="1" customHeight="1">
@@ -3565,22 +3569,22 @@
         <v>21</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="21.6" hidden="1" customHeight="1">
@@ -3588,22 +3592,22 @@
         <v>22</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="21.6" hidden="1" customHeight="1">
@@ -3611,22 +3615,22 @@
         <v>24</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>9</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="21.6" hidden="1" customHeight="1">
@@ -3634,22 +3638,22 @@
         <v>25</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="21.6" hidden="1" customHeight="1">
@@ -3657,22 +3661,22 @@
         <v>25</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="61.5" hidden="1" customHeight="1">
@@ -3680,10 +3684,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>9</v>
@@ -3692,10 +3696,10 @@
         <v>77</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3710,6 +3714,7 @@
   </autoFilter>
   <phoneticPr fontId="40"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3720,12 +3725,12 @@
   <sheetData>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -3734,4 +3739,286 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_x5099__x8003_ xmlns="f98e4964-1bbc-429e-8942-e88792f4a3c1" xsi:nil="true"/>
+    <TaxCatchAll xmlns="c3f6baff-d587-4c1c-bacf-1fb9fe7661e4" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f98e4964-1bbc-429e-8942-e88792f4a3c1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A2BF3CE1CFE90348B5D5A6BC10BEA7DE" ma:contentTypeVersion="19" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="16434ce2c73d2994095f80d393e67ac7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f98e4964-1bbc-429e-8942-e88792f4a3c1" xmlns:ns3="c3f6baff-d587-4c1c-bacf-1fb9fe7661e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cc6f8ce4e3950ea2b7a1e7da09c8c1d3" ns2:_="" ns3:_="">
+    <xsd:import namespace="f98e4964-1bbc-429e-8942-e88792f4a3c1"/>
+    <xsd:import namespace="c3f6baff-d587-4c1c-bacf-1fb9fe7661e4"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:_x5099__x8003_" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f98e4964-1bbc-429e-8942-e88792f4a3c1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="_x5099__x8003_" ma:index="1" nillable="true" ma:displayName="備考" ma:internalName="_x5099__x8003_">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="a4ca2407-f6c7-4c55-87e4-f899293a2642" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="18" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="19" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="24" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c3f6baff-d587-4c1c-bacf-1fb9fe7661e4" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="9" nillable="true" ma:displayName="共有相手" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="10" nillable="true" ma:displayName="共有相手の詳細情報" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="17" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{531f8b7b-e686-4b36-a35d-aca667ec9268}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="c3f6baff-d587-4c1c-bacf-1fb9fe7661e4">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="7" ma:displayName="コンテンツ タイプ"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="2" ma:displayName="タイトル"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE2A25C8-52F3-4B7C-B963-156384C5AC10}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AB4E0F3-17EE-4703-9BF6-3CB9585FBBD0}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{911BE348-77C6-4F1C-A4A8-98780C90B4C4}"/>
 </file>
--- a/90_管理/課題リスト.xlsx
+++ b/90_管理/課題リスト.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{3FECA4D7-415E-46FB-A4DD-52E83F0BD1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCF5BB7C-591C-4837-A13F-7F7CBEF50666}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03407935-CD32-4691-83B6-60A73822E4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="1635" windowWidth="27585" windowHeight="13065" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5145" yWindow="1740" windowWidth="23460" windowHeight="12645" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="課題リスト" sheetId="78" r:id="rId1"/>
@@ -77,12 +77,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="79">
   <si>
     <t>項番</t>
     <rPh sb="0" eb="2">
@@ -322,43 +325,6 @@
     </rPh>
     <rPh sb="50" eb="51">
       <t>ネガ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo UI"/>
-      </rPr>
-      <t xml:space="preserve">①3シート参照
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Meiryo UI"/>
-      </rPr>
-      <t xml:space="preserve">→取込完了メールにトップ画面リンクを追加、とありましたが本システムは新ヒロセWebリンクからのログインになるので、メールからトップ画面リンクを押下してもログインエラーになります。メールからトップ画面リンクは削除して良いでしょうか？⇒新Webログイン画面リンクとする。https://www.hirose.com/ja/product/login
-https://www.hirose.com/en/product/login
-はい、過去メールと口頭にて回答ずみです、上記で問題ございません。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo UI"/>
-      </rPr>
-      <t>②申請完了メールは設計書参照</t>
-    </r>
-  </si>
-  <si>
-    <t>確認中</t>
-    <rPh sb="0" eb="3">
-      <t>カクニンチュウ</t>
     </rPh>
     <phoneticPr fontId="40"/>
   </si>
@@ -1355,6 +1321,13 @@
   <si>
     <t>※こちらのメールに返信はできません。不明な点などございましたら、担当者へお問い合わせください</t>
   </si>
+  <si>
+    <t>①3シート参照
+→取込完了メールにトップ画面リンクを追加、とありましたが本システムは新ヒロセWebリンクからのログインになるので、メールからトップ画面リンクを押下してもログインエラーになります。メールからトップ画面リンクは削除して良いでしょうか？⇒新Webログイン画面リンクとする。https://www.hirose.com/ja/product/login
+https://www.hirose.com/en/product/login
+はい、過去メールと口頭にて回答ずみです、上記で問題ございません。
+②申請完了メールは設計書参照</t>
+  </si>
 </sst>
 </file>
 
@@ -1365,7 +1338,7 @@
     <numFmt numFmtId="177" formatCode="0.00_)"/>
     <numFmt numFmtId="178" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="50">
+  <fonts count="47">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1697,21 +1670,6 @@
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Meiryo UI"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Meiryo UI"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Meiryo UI"/>
     </font>
   </fonts>
   <fills count="13">
@@ -2358,7 +2316,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2394,9 +2352,6 @@
     </xf>
     <xf numFmtId="0" fontId="43" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="186">
@@ -2626,8 +2581,8 @@
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>2686050</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>125067</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3097,11 +3052,11 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.875" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" customWidth="1"/>
-    <col min="5" max="5" width="43.85546875" customWidth="1"/>
+    <col min="3" max="3" width="50.125" customWidth="1"/>
+    <col min="4" max="4" width="9.375" customWidth="1"/>
+    <col min="5" max="5" width="43.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21.6" customHeight="1">
@@ -3173,7 +3128,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="310.5" customHeight="1">
+    <row r="4" spans="1:7" ht="310.5" hidden="1" customHeight="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3186,14 +3141,14 @@
       <c r="D4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="12" t="s">
-        <v>19</v>
+      <c r="E4" s="10" t="s">
+        <v>78</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="24" hidden="1">
@@ -3201,19 +3156,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="F5" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>12</v>
@@ -3224,19 +3179,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="F6" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>12</v>
@@ -3247,19 +3202,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>12</v>
@@ -3270,19 +3225,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>12</v>
@@ -3293,19 +3248,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>12</v>
@@ -3316,22 +3271,22 @@
         <v>10</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="F10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="G10" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="24" hidden="1">
@@ -3339,19 +3294,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D11" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>12</v>
@@ -3362,19 +3317,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="F12" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>12</v>
@@ -3385,19 +3340,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>12</v>
@@ -3408,19 +3363,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="F14" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>12</v>
@@ -3431,19 +3386,19 @@
         <v>15</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>12</v>
@@ -3454,19 +3409,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>12</v>
@@ -3477,19 +3432,19 @@
         <v>17</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D17" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>12</v>
@@ -3500,19 +3455,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D18" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>12</v>
@@ -3523,19 +3478,19 @@
         <v>19</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>12</v>
@@ -3546,19 +3501,19 @@
         <v>20</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="9" t="s">
+      <c r="F20" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>12</v>
@@ -3569,19 +3524,19 @@
         <v>21</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D21" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>12</v>
@@ -3592,19 +3547,19 @@
         <v>22</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D22" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>12</v>
@@ -3615,16 +3570,16 @@
         <v>24</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>9</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>11</v>
@@ -3638,16 +3593,16 @@
         <v>25</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>11</v>
@@ -3661,16 +3616,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>11</v>
@@ -3684,16 +3639,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>11</v>
@@ -3706,7 +3661,6 @@
   <autoFilter ref="A1:G26" xr:uid="{F7D65F84-4143-485E-A686-A2B54498E502}">
     <filterColumn colId="6">
       <filters>
-        <filter val="確認中"/>
         <filter val="検討中"/>
         <filter val="対応中"/>
       </filters>
@@ -3725,12 +3679,12 @@
   <sheetData>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -3742,6 +3696,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_x5099__x8003_ xmlns="f98e4964-1bbc-429e-8942-e88792f4a3c1" xsi:nil="true"/>
@@ -3751,15 +3714,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4012,13 +3966,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE2A25C8-52F3-4B7C-B963-156384C5AC10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AB4E0F3-17EE-4703-9BF6-3CB9585FBBD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AB4E0F3-17EE-4703-9BF6-3CB9585FBBD0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE2A25C8-52F3-4B7C-B963-156384C5AC10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f98e4964-1bbc-429e-8942-e88792f4a3c1"/>
+    <ds:schemaRef ds:uri="c3f6baff-d587-4c1c-bacf-1fb9fe7661e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{911BE348-77C6-4F1C-A4A8-98780C90B4C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{911BE348-77C6-4F1C-A4A8-98780C90B4C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f98e4964-1bbc-429e-8942-e88792f4a3c1"/>
+    <ds:schemaRef ds:uri="c3f6baff-d587-4c1c-bacf-1fb9fe7661e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/90_管理/課題リスト.xlsx
+++ b/90_管理/課題リスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03407935-CD32-4691-83B6-60A73822E4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E519D1-692A-4496-A318-4F024A7F09B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5145" yWindow="1740" windowWidth="23460" windowHeight="12645" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4830" yWindow="255" windowWidth="22440" windowHeight="14475" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="課題リスト" sheetId="78" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="78">
   <si>
     <t>項番</t>
     <rPh sb="0" eb="2">
@@ -249,20 +249,6 @@
     </rPh>
     <rPh sb="28" eb="30">
       <t>ニンシキ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>API受領。
-2026/6/25 仕様確定</t>
-    <rPh sb="3" eb="5">
-      <t>ジュリョウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>カクテイ</t>
     </rPh>
     <phoneticPr fontId="40"/>
   </si>
@@ -589,13 +575,6 @@
   </si>
   <si>
     <t>ヒロセ/AA</t>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>対応中</t>
-    <rPh sb="0" eb="3">
-      <t>タイオウチュウ</t>
-    </rPh>
     <phoneticPr fontId="40"/>
   </si>
   <si>
@@ -1327,6 +1306,55 @@
 https://www.hirose.com/en/product/login
 はい、過去メールと口頭にて回答ずみです、上記で問題ございません。
 ②申請完了メールは設計書参照</t>
+  </si>
+  <si>
+    <t>2026/7/21 新環境証明書はALB⇒コンテナの構成の為、システムのIPはAWS側で変わることが分かりました。AWSのインフラを変更して固定IPを付与させることも出来そうですが、コストが数千円/月かかりそうです。対応方法を相談させてください。</t>
+    <rPh sb="10" eb="13">
+      <t>シンカンキョウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ショウメイショ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>タメ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>コテイ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>デキ</t>
+    </rPh>
+    <rPh sb="95" eb="98">
+      <t>スウセンエン</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="108" eb="110">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
   </si>
 </sst>
 </file>
@@ -2581,8 +2609,8 @@
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>125067</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>25677</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3105,7 +3133,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="24">
+    <row r="3" spans="1:7" ht="48">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -3119,13 +3147,13 @@
         <v>9</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="310.5" hidden="1" customHeight="1">
@@ -3133,16 +3161,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>17</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>11</v>
@@ -3156,19 +3184,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="F5" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>12</v>
@@ -3179,19 +3207,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>26</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>12</v>
@@ -3202,19 +3230,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>12</v>
@@ -3225,19 +3253,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>30</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>12</v>
@@ -3248,45 +3276,45 @@
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="60.75" customHeight="1">
+    <row r="10" spans="1:7" ht="60.75" hidden="1" customHeight="1">
       <c r="A10" s="5">
         <v>10</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="D10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="G10" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="24" hidden="1">
@@ -3294,19 +3322,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>12</v>
@@ -3317,19 +3345,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>42</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>12</v>
@@ -3340,19 +3368,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>12</v>
@@ -3363,19 +3391,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>47</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>12</v>
@@ -3386,19 +3414,19 @@
         <v>15</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>12</v>
@@ -3409,19 +3437,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>12</v>
@@ -3432,19 +3460,19 @@
         <v>17</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>12</v>
@@ -3455,19 +3483,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>12</v>
@@ -3478,19 +3506,19 @@
         <v>19</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>12</v>
@@ -3501,19 +3529,19 @@
         <v>20</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>60</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>12</v>
@@ -3524,19 +3552,19 @@
         <v>21</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>12</v>
@@ -3547,19 +3575,19 @@
         <v>22</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>12</v>
@@ -3570,16 +3598,16 @@
         <v>24</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>9</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>11</v>
@@ -3593,16 +3621,16 @@
         <v>25</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>11</v>
@@ -3616,16 +3644,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>11</v>
@@ -3639,16 +3667,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>11</v>
@@ -3662,7 +3690,6 @@
     <filterColumn colId="6">
       <filters>
         <filter val="検討中"/>
-        <filter val="対応中"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3679,12 +3706,12 @@
   <sheetData>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -3696,15 +3723,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_x5099__x8003_ xmlns="f98e4964-1bbc-429e-8942-e88792f4a3c1" xsi:nil="true"/>
@@ -3714,6 +3732,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3966,20 +3993,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AB4E0F3-17EE-4703-9BF6-3CB9585FBBD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE2A25C8-52F3-4B7C-B963-156384C5AC10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="f98e4964-1bbc-429e-8942-e88792f4a3c1"/>
     <ds:schemaRef ds:uri="c3f6baff-d587-4c1c-bacf-1fb9fe7661e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AB4E0F3-17EE-4703-9BF6-3CB9585FBBD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/90_管理/課題リスト.xlsx
+++ b/90_管理/課題リスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E519D1-692A-4496-A318-4F024A7F09B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71561918-54E1-47E3-8436-BB4FD8D3430B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4830" yWindow="255" windowWidth="22440" windowHeight="14475" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1308,7 +1308,7 @@
 ②申請完了メールは設計書参照</t>
   </si>
   <si>
-    <t>2026/7/21 新環境証明書はALB⇒コンテナの構成の為、システムのIPはAWS側で変わることが分かりました。AWSのインフラを変更して固定IPを付与させることも出来そうですが、コストが数千円/月かかりそうです。対応方法を相談させてください。</t>
+    <t>2026/7/21 新環境証明書はALB⇒コンテナの構成の為、システムのIPはAWS側で変わることが分かりました。AWSのインフラを変更して固定IPを付与させることも出来そうですが、コストが数千円/月かかりそうです。他の方法ないか検討中です。</t>
     <rPh sb="10" eb="13">
       <t>シンカンキョウ</t>
     </rPh>
@@ -1348,8 +1348,8 @@
     <rPh sb="99" eb="100">
       <t>ツキ</t>
     </rPh>
-    <rPh sb="108" eb="110">
-      <t>タイオウ</t>
+    <rPh sb="108" eb="109">
+      <t>ホカ</t>
     </rPh>
     <rPh sb="110" eb="112">
       <t>ホウホウ</t>
@@ -3723,6 +3723,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_x5099__x8003_ xmlns="f98e4964-1bbc-429e-8942-e88792f4a3c1" xsi:nil="true"/>
@@ -3732,15 +3741,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3993,20 +3993,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AB4E0F3-17EE-4703-9BF6-3CB9585FBBD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE2A25C8-52F3-4B7C-B963-156384C5AC10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="f98e4964-1bbc-429e-8942-e88792f4a3c1"/>
     <ds:schemaRef ds:uri="c3f6baff-d587-4c1c-bacf-1fb9fe7661e4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AB4E0F3-17EE-4703-9BF6-3CB9585FBBD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/90_管理/課題リスト.xlsx
+++ b/90_管理/課題リスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71561918-54E1-47E3-8436-BB4FD8D3430B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9CB064-55D6-489F-A549-A5D12D2F69F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4830" yWindow="255" windowWidth="22440" windowHeight="14475" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -253,9 +253,16 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
-    <t>検討中</t>
-    <rPh sb="0" eb="3">
-      <t>ケントウチュウ</t>
+    <t>API受領。
+2026/6/25 仕様確定</t>
+    <rPh sb="3" eb="5">
+      <t>ジュリョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カクテイ</t>
     </rPh>
     <phoneticPr fontId="40"/>
   </si>
@@ -575,6 +582,13 @@
   </si>
   <si>
     <t>ヒロセ/AA</t>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>対応中</t>
+    <rPh sb="0" eb="3">
+      <t>タイオウチュウ</t>
+    </rPh>
     <phoneticPr fontId="40"/>
   </si>
   <si>
@@ -1306,55 +1320,6 @@
 https://www.hirose.com/en/product/login
 はい、過去メールと口頭にて回答ずみです、上記で問題ございません。
 ②申請完了メールは設計書参照</t>
-  </si>
-  <si>
-    <t>2026/7/21 新環境証明書はALB⇒コンテナの構成の為、システムのIPはAWS側で変わることが分かりました。AWSのインフラを変更して固定IPを付与させることも出来そうですが、コストが数千円/月かかりそうです。他の方法ないか検討中です。</t>
-    <rPh sb="10" eb="13">
-      <t>シンカンキョウ</t>
-    </rPh>
-    <rPh sb="13" eb="16">
-      <t>ショウメイショ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>コウセイ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>タメ</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>ガワ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="66" eb="68">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>コテイ</t>
-    </rPh>
-    <rPh sb="75" eb="77">
-      <t>フヨ</t>
-    </rPh>
-    <rPh sb="83" eb="85">
-      <t>デキ</t>
-    </rPh>
-    <rPh sb="95" eb="98">
-      <t>スウセンエン</t>
-    </rPh>
-    <rPh sb="99" eb="100">
-      <t>ツキ</t>
-    </rPh>
-    <rPh sb="108" eb="109">
-      <t>ホカ</t>
-    </rPh>
-    <rPh sb="110" eb="112">
-      <t>ホウホウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
   </si>
 </sst>
 </file>
@@ -2610,7 +2575,7 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>25677</xdr:rowOff>
+      <xdr:rowOff>25676</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3133,7 +3098,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="48">
+    <row r="3" spans="1:7" ht="24">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -3147,13 +3112,13 @@
         <v>9</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="310.5" hidden="1" customHeight="1">
@@ -3170,7 +3135,7 @@
         <v>9</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>11</v>
@@ -3325,13 +3290,13 @@
         <v>32</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>22</v>
@@ -3345,16 +3310,16 @@
         <v>12</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>22</v>
@@ -3368,16 +3333,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>20</v>
@@ -3391,16 +3356,16 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>22</v>
@@ -3414,16 +3379,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>22</v>
@@ -3437,16 +3402,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>22</v>
@@ -3460,16 +3425,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>22</v>
@@ -3483,16 +3448,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>22</v>
@@ -3506,16 +3471,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>22</v>
@@ -3529,16 +3494,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>22</v>
@@ -3552,16 +3517,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>22</v>
@@ -3575,16 +3540,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>22</v>
@@ -3598,16 +3563,16 @@
         <v>24</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>9</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>11</v>
@@ -3621,16 +3586,16 @@
         <v>25</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>11</v>
@@ -3644,16 +3609,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>11</v>
@@ -3667,16 +3632,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>11</v>
@@ -3689,7 +3654,7 @@
   <autoFilter ref="A1:G26" xr:uid="{F7D65F84-4143-485E-A686-A2B54498E502}">
     <filterColumn colId="6">
       <filters>
-        <filter val="検討中"/>
+        <filter val="対応中"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3706,12 +3671,12 @@
   <sheetData>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -3723,15 +3688,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_x5099__x8003_ xmlns="f98e4964-1bbc-429e-8942-e88792f4a3c1" xsi:nil="true"/>
@@ -3741,6 +3697,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3993,20 +3958,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AB4E0F3-17EE-4703-9BF6-3CB9585FBBD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE2A25C8-52F3-4B7C-B963-156384C5AC10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="f98e4964-1bbc-429e-8942-e88792f4a3c1"/>
     <ds:schemaRef ds:uri="c3f6baff-d587-4c1c-bacf-1fb9fe7661e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AB4E0F3-17EE-4703-9BF6-3CB9585FBBD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
